--- a/Casos.xlsx
+++ b/Casos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pc\Desktop\SOFT311\PROYECTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1979FB71-43D3-44D9-9356-4BFCB2696C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9351A0B8-4F7E-47A1-AB62-642ECFAAE8DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-6855" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TC-001 Sign Up" sheetId="25" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="77">
   <si>
     <t>Pasos</t>
   </si>
@@ -122,9 +122,6 @@
     <t>Registrarse correctamente</t>
   </si>
   <si>
-    <t>Añadir productos al favorito</t>
-  </si>
-  <si>
     <t>All Products</t>
   </si>
   <si>
@@ -147,9 +144,6 @@
   </si>
   <si>
     <t>TC-007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validar redirección a Checkout con éxito </t>
   </si>
   <si>
     <t>Validar cantidad del elemnetos agregado a favoritos con éxito</t>
@@ -225,12 +219,105 @@
   <si>
     <t>Poder registrarse correctamente</t>
   </si>
+  <si>
+    <t>Ir en la página https://storedemo.testdino.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Estar en la página https://storedemo.testdino.com/
+2. Dar click en el botón Shop Now
+3. 
+4. 
+5. </t>
+  </si>
+  <si>
+    <t>Exitoso, el botón redirecciono a los productos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Media </t>
+  </si>
+  <si>
+    <t>Añadir productos a favorito</t>
+  </si>
+  <si>
+    <t>Ir a la pagina https://storedemo.testdino.com/products</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.  Estar en la página https://storedemo.testdino.com/products
+2.  Poner mouse sobre un producto
+3.  Dar click en botón de favorito (corazón)
+4. 
+5. </t>
+  </si>
+  <si>
+    <t>Exitoso, el producto se agrega con éxito, sube el identificador de favoritos</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>si</t>
+  </si>
+  <si>
+    <t>Ir a la página https://storedemo.testdino.com/about-us</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1.  Estar en la página https://storedemo.testdino.com/about-us
+2. Validar que los textos de la misión sean 
+        1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="3" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>At TestDino Demo Store, our mission is to make cutting-edge technology accessible to everyone. We believe that quality electronics and innovative gadgets should enhance your daily life, whether you're working, creating, or simply staying connected with loved ones.
+         2. We're committed to providing exceptional customer service, competitive pricing, and a curated selection of the latest tech products. From premium laptops and smartphones to smart home devices and audio equipment, we carefully select each product to ensure it meets our high standards of quality and innovation.
+         3. We're more than just an online store—we're your trusted technology partner. Our expert team is dedicated to helping you find the perfect products for your needs, backed by comprehensive product information, honest reviews, and reliable support every step of the way.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Exitoso, el texto es consiso </t>
+  </si>
+  <si>
+    <t>Ir a la página https://storedemo.testdino.com/contact-us</t>
+  </si>
+  <si>
+    <t>1.  Estar en la página https://storedemo.testdino.com/contact-us
+2. Ingresar First Name
+3. Ingresar Last Name
+4. Ingresar Subject
+5. Escribir el mensaje
+6. Dar click en botón Send Message</t>
+  </si>
+  <si>
+    <t>Exitoso, el mensaje se envía correctamente</t>
+  </si>
+  <si>
+    <t>Ir a la página https://storedemo.testdino.com</t>
+  </si>
+  <si>
+    <t>Validar redirección de Start Shopping con éxito, en Cart modal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Estar en la página https://storedemo.testdino.com
+2. Dar click al botón carrito (arriba a la derecha)
+3. Dar click al botón Start Shopping
+4. 
+5. </t>
+  </si>
+  <si>
+    <t>Exitoso, si se redirecciona a la página de los productos, sin embargo no se marca la opción del menú superior correctamente</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -242,6 +329,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="3" tint="-0.249977111117893"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -673,7 +767,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -681,7 +775,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -689,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -697,7 +791,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -736,7 +830,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -819,7 +913,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -902,7 +996,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -985,7 +1079,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1068,7 +1162,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1098,7 +1192,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -1106,7 +1200,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1114,7 +1208,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1122,7 +1216,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1130,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1138,7 +1232,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1161,7 +1255,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1190,7 +1284,9 @@
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
@@ -1203,26 +1299,32 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="1"/>
+      <c r="B9" s="1" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="1"/>
+      <c r="B10" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1244,7 +1346,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1252,7 +1354,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1260,7 +1362,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1273,7 +1375,9 @@
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
@@ -1286,26 +1390,32 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="1"/>
+      <c r="B9" s="1" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="1"/>
+      <c r="B10" s="1" t="s">
+        <v>66</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1327,7 +1437,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1335,7 +1445,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1343,7 +1453,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1356,7 +1466,9 @@
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
@@ -1364,31 +1476,37 @@
       </c>
       <c r="B6" s="1"/>
     </row>
-    <row r="7" spans="1:2" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="195" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="1"/>
+      <c r="B9" s="1" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="1"/>
+      <c r="B10" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1410,7 +1528,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1418,7 +1536,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1426,7 +1544,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1439,7 +1557,9 @@
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
@@ -1452,26 +1572,32 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>14</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="1"/>
+      <c r="B9" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="1"/>
+      <c r="B10" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1485,7 +1611,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="86.85546875" customWidth="1"/>
+    <col min="2" max="2" width="112.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1493,7 +1619,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1501,7 +1627,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1509,7 +1635,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1522,7 +1648,9 @@
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
@@ -1535,26 +1663,32 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="1"/>
+      <c r="B9" s="1" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="1"/>
+      <c r="B10" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1576,7 +1710,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1592,7 +1726,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1659,7 +1793,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">

--- a/Casos.xlsx
+++ b/Casos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pc\Desktop\SOFT311\PROYECTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9351A0B8-4F7E-47A1-AB62-642ECFAAE8DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C18EE0E3-87FB-4E8C-9F5B-62CEAADAE374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" firstSheet="10" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TC-001 Sign Up" sheetId="25" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="95">
   <si>
     <t>Pasos</t>
   </si>
@@ -76,13 +76,6 @@
     <t>Login</t>
   </si>
   <si>
-    <t xml:space="preserve">1. 
-2. 
-3. 
-4. 
-5. </t>
-  </si>
-  <si>
     <t xml:space="preserve">Validación de formato email en suscripción </t>
   </si>
   <si>
@@ -144,9 +137,6 @@
   </si>
   <si>
     <t>TC-007</t>
-  </si>
-  <si>
-    <t>Validar cantidad del elemnetos agregado a favoritos con éxito</t>
   </si>
   <si>
     <t>TC-008</t>
@@ -312,12 +302,112 @@
   <si>
     <t>Exitoso, si se redirecciona a la página de los productos, sin embargo no se marca la opción del menú superior correctamente</t>
   </si>
+  <si>
+    <t>Validar cantidad del elementos agregados a favoritos con éxito, desde página All products</t>
+  </si>
+  <si>
+    <t>Ir a la página https://storedemo.testdino.com/products</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.  Estar en la pagina https://storedemo.testdino.com/products
+2.  Agregar productos a favoritos dando click en el botón de corazón
+3.  Validar la cantidad de productos agregados a favoritos (en la esquina derecha arriba en el ícono de corazón)
+4. 
+5. </t>
+  </si>
+  <si>
+    <t>Exitoso, se muestra correctamente la cantidad de favoritos</t>
+  </si>
+  <si>
+    <t>Ir a la página https://storedemo.testdino.com/login</t>
+  </si>
+  <si>
+    <t>email: nayelicastillo
+password:123456</t>
+  </si>
+  <si>
+    <t>Exitoso, muestra mensaje correcto</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1.  Estar en la página https://storedemo.testdino.com/login
+2.  Ingresar email: nayelicastillo
+3.  Ingresar contraseña: 123456
+4.  Dar click en botón sign in
+5.  Validar que diga </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>email is invalid</t>
+    </r>
+  </si>
+  <si>
+    <t>Ir a la página https://storedemo.testdino.com/</t>
+  </si>
+  <si>
+    <t>Your Email: 12345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Estar en la página https://storedemo.testdino.com en la sección Suscribe
+2.  Ingresar Your Email: 12345
+3.  Dar click en botón Suscribe
+4.  Validar que no lo deje suscribir 
+5. </t>
+  </si>
+  <si>
+    <t>Exitoso, se espera que no permita que se suscriba, pero si lo permite</t>
+  </si>
+  <si>
+    <t>First Name: Nayeli
+Last Name: Castillo
+Subject: consulta
+Your Message: Hoy abren</t>
+  </si>
+  <si>
+    <t>1.  Estar en la página https://storedemo.testdino.com/contact-us
+2.  Ingresar Firts Name, Last Name, Subject
+3.  Escribir Your Message
+4.  Dar click en botón Send Message
+5.  Validar que no permita enviar mensaje con menos de 10 caracteres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exitoso, no permite enviar mensaje con menos de 10 caracteres </t>
+  </si>
+  <si>
+    <t>Exitoso, no lo permite y muestra el mensaje correctamente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validación de remover producto favorito con éxito </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.  Estar en la página https://storedemo.testdino.com/products
+2.  Dar click en botón de agregar al carrito ( botón de bolsa), del card de un producto
+3.  Al mismo producto volver a darle click al botón de la bolsa
+4.  Validar que muestre el mensaje: Already added!
+5. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.  Estar en la página https://storedemo.testdino.com/products
+2.  Dar click en botón de agregar  a favorito (botón de corazón), del card de un producto
+3.  Dar click de nuevo en botón de favorito (botón de corazón), del mismo producto
+4.  Validar que muestre la alerta de "Removed from wishlist"
+5. </t>
+  </si>
+  <si>
+    <t>Exitoso, muestra el mensaje correctamente</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -336,6 +426,13 @@
     <font>
       <sz val="11"/>
       <color theme="3" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5" tint="-0.499984740745262"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -745,7 +842,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -753,7 +850,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -767,7 +864,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -775,7 +872,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -783,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -791,7 +888,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -830,7 +927,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -838,7 +935,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -846,7 +943,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -859,39 +956,49 @@
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="1"/>
+      <c r="B6" s="1" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="7" spans="1:2" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>14</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="1"/>
+      <c r="B9" s="1" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="1"/>
+      <c r="B10" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -913,7 +1020,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -921,7 +1028,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -929,7 +1036,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -942,39 +1049,49 @@
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="1"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="1"/>
+      <c r="B6" s="3" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="7" spans="1:2" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>14</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="1"/>
+      <c r="B9" s="1" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="1"/>
+      <c r="B10" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -996,7 +1113,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1004,7 +1121,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1012,7 +1129,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1025,7 +1142,9 @@
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
@@ -1038,26 +1157,32 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>14</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="1"/>
+      <c r="B9" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="1"/>
+      <c r="B10" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1079,7 +1204,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1087,7 +1212,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1095,7 +1220,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1108,7 +1233,9 @@
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
@@ -1121,26 +1248,32 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>14</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="1"/>
+      <c r="B9" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="1"/>
+      <c r="B10" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1162,7 +1295,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1178,7 +1311,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1192,7 +1325,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -1200,7 +1333,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1208,7 +1341,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1216,7 +1349,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1224,7 +1357,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1232,7 +1365,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1255,7 +1388,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1263,7 +1396,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1271,7 +1404,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1285,7 +1418,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1299,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1307,7 +1440,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1315,7 +1448,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1346,7 +1479,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1354,7 +1487,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1362,7 +1495,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1376,7 +1509,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1390,7 +1523,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1398,7 +1531,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1406,7 +1539,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1414,7 +1547,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1437,7 +1570,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1445,7 +1578,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1453,7 +1586,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1467,7 +1600,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1481,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1489,7 +1622,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1497,7 +1630,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1528,7 +1661,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1536,7 +1669,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1544,7 +1677,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1558,7 +1691,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1572,7 +1705,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1580,7 +1713,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1619,7 +1752,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1627,7 +1760,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1635,7 +1768,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1649,7 +1782,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1663,7 +1796,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1671,7 +1804,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1679,7 +1812,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1710,7 +1843,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1718,7 +1851,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1726,7 +1859,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1739,7 +1872,9 @@
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
@@ -1752,26 +1887,32 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>14</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="1"/>
+      <c r="B9" s="1" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="1"/>
+      <c r="B10" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1793,7 +1934,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1809,7 +1950,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1822,39 +1963,49 @@
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="1"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="1"/>
+      <c r="B6" s="3" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="7" spans="1:2" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="1"/>
+      <c r="B9" s="1" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="1"/>
+      <c r="B10" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Casos.xlsx
+++ b/Casos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pc\Desktop\SOFT311\PROYECTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C18EE0E3-87FB-4E8C-9F5B-62CEAADAE374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C80BFCC-DB42-4AFC-8BEE-2BE7550F44AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" firstSheet="10" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" firstSheet="7" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TC-001 Sign Up" sheetId="25" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="96">
   <si>
     <t>Pasos</t>
   </si>
@@ -76,9 +76,6 @@
     <t>Login</t>
   </si>
   <si>
-    <t xml:space="preserve">Validación de formato email en suscripción </t>
-  </si>
-  <si>
     <t>Ingreso a la pantalla de productos por medio del botón Shop Now</t>
   </si>
   <si>
@@ -131,9 +128,6 @@
   </si>
   <si>
     <t>TC-006</t>
-  </si>
-  <si>
-    <t>Cart</t>
   </si>
   <si>
     <t>TC-007</t>
@@ -284,9 +278,6 @@
 6. Dar click en botón Send Message</t>
   </si>
   <si>
-    <t>Exitoso, el mensaje se envía correctamente</t>
-  </si>
-  <si>
     <t>Ir a la página https://storedemo.testdino.com</t>
   </si>
   <si>
@@ -303,17 +294,7 @@
     <t>Exitoso, si se redirecciona a la página de los productos, sin embargo no se marca la opción del menú superior correctamente</t>
   </si>
   <si>
-    <t>Validar cantidad del elementos agregados a favoritos con éxito, desde página All products</t>
-  </si>
-  <si>
     <t>Ir a la página https://storedemo.testdino.com/products</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.  Estar en la pagina https://storedemo.testdino.com/products
-2.  Agregar productos a favoritos dando click en el botón de corazón
-3.  Validar la cantidad de productos agregados a favoritos (en la esquina derecha arriba en el ícono de corazón)
-4. 
-5. </t>
   </si>
   <si>
     <t>Exitoso, se muestra correctamente la cantidad de favoritos</t>
@@ -351,19 +332,6 @@
     <t>Ir a la página https://storedemo.testdino.com/</t>
   </si>
   <si>
-    <t>Your Email: 12345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Estar en la página https://storedemo.testdino.com en la sección Suscribe
-2.  Ingresar Your Email: 12345
-3.  Dar click en botón Suscribe
-4.  Validar que no lo deje suscribir 
-5. </t>
-  </si>
-  <si>
-    <t>Exitoso, se espera que no permita que se suscriba, pero si lo permite</t>
-  </si>
-  <si>
     <t>First Name: Nayeli
 Last Name: Castillo
 Subject: consulta
@@ -401,6 +369,45 @@
   </si>
   <si>
     <t>Exitoso, muestra el mensaje correctamente</t>
+  </si>
+  <si>
+    <t>First Name: Nayeli
+Last Name: Castillo
+Subject: consulta 
+Your Message: Hola, me pueden brindar el número de télefono, por favor.</t>
+  </si>
+  <si>
+    <t>Exitoso, el mensaje se envía correctamente y muestra un mesaje de éxito</t>
+  </si>
+  <si>
+    <t>Cart - Home</t>
+  </si>
+  <si>
+    <t>Validar remover favorito desde pagina de wishlist</t>
+  </si>
+  <si>
+    <t>1.  Estar en la pagina https://storedemo.testdino.com/products
+2.  Agregar productos a favoritos dando click en el botón de corazón
+3.  Dar click en el icono de corazon para redirigirse a la pantalla https://storedemo.testdino.com/wishlist
+4. Validar que se este en la pantalla de wishlist
+5. Dar click en el icono de borrar de un card de producto
+6. Validar que se remueve el producto por medio del mensaje</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validación de suscripción </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Estar en la página https://storedemo.testdino.com en la sección Suscribe
+2.  Ingresar Your Email: naye2@test.com
+3.  Dar click en botón Suscribe
+4.  Validar que se suscriba el email 
+5. </t>
+  </si>
+  <si>
+    <t>Exitoso, se suscribio correctamente</t>
+  </si>
+  <si>
+    <t>Your Email: naye2@test.com</t>
   </si>
 </sst>
 </file>
@@ -842,7 +849,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -850,7 +857,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -864,7 +871,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -872,7 +879,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -880,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -888,7 +895,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -927,7 +934,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -935,7 +942,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -943,7 +950,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -957,7 +964,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -965,7 +972,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -973,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -981,7 +988,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -989,7 +996,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1020,7 +1027,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1028,7 +1035,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1036,7 +1043,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1050,7 +1057,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -1058,7 +1065,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1066,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1074,7 +1081,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1082,7 +1089,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1113,7 +1120,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1121,7 +1128,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1129,7 +1136,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1143,7 +1150,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1157,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1165,7 +1172,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1204,7 +1211,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1212,7 +1219,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1220,7 +1227,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1234,7 +1241,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1248,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1256,7 +1263,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1295,7 +1302,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1311,7 +1318,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1325,7 +1332,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -1333,7 +1340,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1341,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1349,7 +1356,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1357,7 +1364,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1365,7 +1372,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1388,7 +1395,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1396,7 +1403,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1404,7 +1411,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1418,7 +1425,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1432,7 +1439,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1440,7 +1447,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1448,7 +1455,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1479,7 +1486,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1487,7 +1494,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1495,7 +1502,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1509,7 +1516,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1523,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1531,7 +1538,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1539,7 +1546,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1547,7 +1554,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1570,7 +1577,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1578,7 +1585,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1586,7 +1593,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1600,7 +1607,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1614,7 +1621,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1622,7 +1629,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1630,7 +1637,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1661,7 +1668,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1669,7 +1676,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1677,7 +1684,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1691,21 +1698,23 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="1"/>
-    </row>
-    <row r="7" spans="1:2" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1713,7 +1722,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1752,7 +1761,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1760,7 +1769,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1768,7 +1777,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1782,7 +1791,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1796,7 +1805,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1804,7 +1813,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1812,7 +1821,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1835,7 +1844,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="86.85546875" customWidth="1"/>
+    <col min="2" max="2" width="96.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1843,7 +1852,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1851,7 +1860,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1859,7 +1868,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1873,7 +1882,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1882,12 +1891,12 @@
       </c>
       <c r="B6" s="1"/>
     </row>
-    <row r="7" spans="1:2" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="94.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1895,7 +1904,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1903,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1934,7 +1943,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1950,7 +1959,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1964,7 +1973,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -1972,7 +1981,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1980,7 +1989,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1988,7 +1997,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1996,7 +2005,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">

--- a/Casos.xlsx
+++ b/Casos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pc\Desktop\SOFT311\PROYECTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C80BFCC-DB42-4AFC-8BEE-2BE7550F44AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FCCF4C4-E160-4056-92C4-7D93A268051A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" firstSheet="7" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" firstSheet="10" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TC-001 Sign Up" sheetId="25" r:id="rId1"/>
@@ -332,12 +332,6 @@
     <t>Ir a la página https://storedemo.testdino.com/</t>
   </si>
   <si>
-    <t>First Name: Nayeli
-Last Name: Castillo
-Subject: consulta
-Your Message: Hoy abren</t>
-  </si>
-  <si>
     <t>1.  Estar en la página https://storedemo.testdino.com/contact-us
 2.  Ingresar Firts Name, Last Name, Subject
 3.  Escribir Your Message
@@ -408,6 +402,12 @@
   </si>
   <si>
     <t>Your Email: naye2@test.com</t>
+  </si>
+  <si>
+    <t>First Name: Nayeli
+Last Name: Castillo
+Subject: Consulta
+Your Message: Hola.</t>
   </si>
 </sst>
 </file>
@@ -950,7 +950,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -972,7 +972,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -988,7 +988,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1065,7 +1065,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1073,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1081,7 +1081,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1172,7 +1172,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1227,7 +1227,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1263,7 +1263,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1706,7 +1706,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -1722,7 +1722,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1769,7 +1769,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1868,7 +1868,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1896,7 +1896,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">

--- a/Casos.xlsx
+++ b/Casos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pc\Desktop\SOFT311\PROYECTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FCCF4C4-E160-4056-92C4-7D93A268051A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E55848E-2FCB-4C4B-958D-5731BEEA019F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" firstSheet="10" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="109">
   <si>
     <t>Pasos</t>
   </si>
@@ -122,9 +122,6 @@
   </si>
   <si>
     <t>Contac Us</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validar envío de mensaje con éxito </t>
   </si>
   <si>
     <t>TC-006</t>
@@ -243,25 +240,6 @@
   </si>
   <si>
     <t>Ir a la página https://storedemo.testdino.com/about-us</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1.  Estar en la página https://storedemo.testdino.com/about-us
-2. Validar que los textos de la misión sean 
-        1. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="3" tint="-0.249977111117893"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>At TestDino Demo Store, our mission is to make cutting-edge technology accessible to everyone. We believe that quality electronics and innovative gadgets should enhance your daily life, whether you're working, creating, or simply staying connected with loved ones.
-         2. We're committed to providing exceptional customer service, competitive pricing, and a curated selection of the latest tech products. From premium laptops and smartphones to smart home devices and audio equipment, we carefully select each product to ensure it meets our high standards of quality and innovation.
-         3. We're more than just an online store—we're your trusted technology partner. Our expert team is dedicated to helping you find the perfect products for your needs, backed by comprehensive product information, honest reviews, and reliable support every step of the way.</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">Exitoso, el texto es consiso </t>
@@ -282,13 +260,6 @@
   </si>
   <si>
     <t>Validar redirección de Start Shopping con éxito, en Cart modal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Estar en la página https://storedemo.testdino.com
-2. Dar click al botón carrito (arriba a la derecha)
-3. Dar click al botón Start Shopping
-4. 
-5. </t>
   </si>
   <si>
     <t>Exitoso, si se redirecciona a la página de los productos, sin embargo no se marca la opción del menú superior correctamente</t>
@@ -345,26 +316,6 @@
     <t>Exitoso, no lo permite y muestra el mensaje correctamente</t>
   </si>
   <si>
-    <t xml:space="preserve">Validación de remover producto favorito con éxito </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.  Estar en la página https://storedemo.testdino.com/products
-2.  Dar click en botón de agregar al carrito ( botón de bolsa), del card de un producto
-3.  Al mismo producto volver a darle click al botón de la bolsa
-4.  Validar que muestre el mensaje: Already added!
-5. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.  Estar en la página https://storedemo.testdino.com/products
-2.  Dar click en botón de agregar  a favorito (botón de corazón), del card de un producto
-3.  Dar click de nuevo en botón de favorito (botón de corazón), del mismo producto
-4.  Validar que muestre la alerta de "Removed from wishlist"
-5. </t>
-  </si>
-  <si>
-    <t>Exitoso, muestra el mensaje correctamente</t>
-  </si>
-  <si>
     <t>First Name: Nayeli
 Last Name: Castillo
 Subject: consulta 
@@ -388,26 +339,109 @@
 6. Validar que se remueve el producto por medio del mensaje</t>
   </si>
   <si>
-    <t xml:space="preserve">Validación de suscripción </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Estar en la página https://storedemo.testdino.com en la sección Suscribe
-2.  Ingresar Your Email: naye2@test.com
-3.  Dar click en botón Suscribe
-4.  Validar que se suscriba el email 
-5. </t>
-  </si>
-  <si>
-    <t>Exitoso, se suscribio correctamente</t>
-  </si>
-  <si>
-    <t>Your Email: naye2@test.com</t>
-  </si>
-  <si>
     <t>First Name: Nayeli
 Last Name: Castillo
 Subject: Consulta
 Your Message: Hola.</t>
+  </si>
+  <si>
+    <t>Validación de agregar un producto a favoritos dos veces</t>
+  </si>
+  <si>
+    <t>Verificar que el sistema no permita duplicar un producto en la lista de favoritos</t>
+  </si>
+  <si>
+    <t>1.  Estar en la página https://storedemo.testdino.com/products
+2.  Dar click en botón de agregar  a favorito (botón de corazón), del card de un producto
+3.  Dar click de nuevo en botón de favorito (botón de corazón), del mismo producto
+4.  Revisar el comportamiento del sistema.</t>
+  </si>
+  <si>
+    <t>El producto no se duplica en favoritos y el sistema muestra un mensaje apropiado</t>
+  </si>
+  <si>
+    <t>Validación de suscripción con formato de email inválido</t>
+  </si>
+  <si>
+    <t>Verificar que el sistema no permita suscribirse con un correo electrónico inválido</t>
+  </si>
+  <si>
+    <t>El sistema muestra un mensaje de validación indicando que el formato del correo es inválido y no permite la suscripción</t>
+  </si>
+  <si>
+    <t>Your Email: nayelicastillo</t>
+  </si>
+  <si>
+    <t>1. Estar en la página https://storedemo.testdino.com en la sección Suscribe
+2. Ingresar Your Email: nayelicastillo
+3. Dar click en botón Suscribe
+4. Validar la respuesta del sistema</t>
+  </si>
+  <si>
+    <t>Validar hacer un registro de un user correctamente</t>
+  </si>
+  <si>
+    <t>Poder ingresar con un usuario existente en el sistema</t>
+  </si>
+  <si>
+    <t>Validar redirect de boton Shop Now</t>
+  </si>
+  <si>
+    <t>Poder agregar a favoritos productos</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1.  Estar en la página https://storedemo.testdino.com/about-us
+2. Validar que los textos de la misión sean 
+     </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="3" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">   1. At TestDino Demo Store, our mission is to make cutting-edge technology accessible to everyone. We believe that quality electronics and innovative gadgets should enhance your daily life, whether you're working, creating, or simply staying connected with loved ones.
+         2. We're committed to providing exceptional customer service, competitive pricing, and a curated selection of the latest tech products. From premium laptops and smartphones to smart home devices and audio equipment, we carefully select each product to ensure it meets our high standards of quality and innovation.
+         3. We're more than just an online store—we're your trusted technology partner. Our expert team is dedicated to helping you find the perfect products for your needs, backed by comprehensive product information, honest reviews, and reliable support every step of the way.</t>
+    </r>
+  </si>
+  <si>
+    <t>Validacion de textos consistentes sin modificacion en el tiempo</t>
+  </si>
+  <si>
+    <t>Poder enviar un mensaje para contactar con la empresa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validar envío de mensaje de contacto con éxito </t>
+  </si>
+  <si>
+    <t>Validar redirección del boton Start Shopping</t>
+  </si>
+  <si>
+    <t>1. Estar en la página https://storedemo.testdino.com
+2. Dar click al botón carrito (arriba a la derecha)
+3. Dar click al botón Start Shopping</t>
+  </si>
+  <si>
+    <t>Poder remover un producto favorito</t>
+  </si>
+  <si>
+    <t>Validar no poder ingresar con email con formato invalido</t>
+  </si>
+  <si>
+    <t>No poder enviar mensajes de cotacto con un mensaje inferior a 10 caracteres</t>
+  </si>
+  <si>
+    <t>1.  Estar en la página https://storedemo.testdino.com/products
+2.  Dar click en botón de agregar al carrito ( botón de bolsa), del card de un producto
+3.  Al mismo producto volver a darle click al botón de la bolsa
+4.  Validar que muestre el mensaje: Already added!</t>
+  </si>
+  <si>
+    <t>Poder validar no agregar productos duplicados al carrito</t>
   </si>
 </sst>
 </file>
@@ -480,7 +514,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -490,6 +524,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -864,14 +902,16 @@
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -879,7 +919,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -887,7 +927,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -895,7 +935,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -934,7 +974,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -949,22 +989,24 @@
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>91</v>
+      <c r="B3" s="4" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="1"/>
+      <c r="B4" s="4" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -972,23 +1014,23 @@
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>93</v>
+      <c r="B8" s="5" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -996,7 +1038,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1027,7 +1069,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1050,14 +1092,16 @@
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -1065,7 +1109,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1073,7 +1117,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1081,7 +1125,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1089,7 +1133,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1120,7 +1164,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1143,14 +1187,16 @@
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1164,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1172,7 +1218,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1211,7 +1257,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1226,22 +1272,24 @@
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>82</v>
+      <c r="B3" s="4" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="1"/>
+      <c r="B4" s="4" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1250,20 +1298,20 @@
       </c>
       <c r="B6" s="1"/>
     </row>
-    <row r="7" spans="1:2" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>85</v>
+      <c r="B8" s="4" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1302,7 +1350,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1325,14 +1373,16 @@
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -1340,7 +1390,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1348,7 +1398,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1356,7 +1406,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1364,7 +1414,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1372,7 +1422,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1395,7 +1445,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1418,14 +1468,16 @@
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1439,7 +1491,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1447,7 +1499,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1455,7 +1507,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1486,7 +1538,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1502,21 +1554,23 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1530,7 +1584,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1538,7 +1592,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1546,7 +1600,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1554,7 +1608,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1577,7 +1631,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1600,14 +1654,16 @@
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1621,7 +1677,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>64</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1629,7 +1685,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1637,7 +1693,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1668,7 +1724,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1684,21 +1740,23 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>30</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -1706,7 +1764,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -1714,7 +1772,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1722,7 +1780,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1761,7 +1819,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1769,7 +1827,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1777,21 +1835,23 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1800,12 +1860,12 @@
       </c>
       <c r="B6" s="1"/>
     </row>
-    <row r="7" spans="1:2" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1813,7 +1873,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1821,7 +1881,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1852,7 +1912,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1868,21 +1928,23 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1896,7 +1958,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1904,7 +1966,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1912,7 +1974,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1943,7 +2005,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1966,14 +2028,16 @@
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -1981,7 +2045,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1989,7 +2053,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1997,7 +2061,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2005,7 +2069,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
